--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -10461,7 +10461,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆两江新区交付中心</t>
+          <t>小鹏汽车重庆二郎销售中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>重庆市九龙坡区石新路172号附2号</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆二郎销售中心</t>
+          <t>小鹏汽车重庆两江新区交付中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区石新路172号附2号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11832,17 +11832,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11852,29 +11852,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11884,29 +11884,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -11933,12 +11933,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11948,29 +11948,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11980,29 +11980,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
@@ -12024,17 +12024,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12044,29 +12044,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
         </is>
       </c>
     </row>
@@ -12088,17 +12088,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
@@ -12120,17 +12120,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12140,29 +12140,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12172,29 +12172,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12236,29 +12236,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
@@ -12280,17 +12280,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12300,29 +12300,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12332,29 +12332,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12364,29 +12364,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
@@ -12408,17 +12408,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
@@ -12467,22 +12467,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12492,29 +12492,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
         </is>
       </c>
     </row>
@@ -12536,17 +12536,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12556,29 +12556,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12588,29 +12588,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12627,22 +12627,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12659,22 +12659,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12691,22 +12691,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12723,22 +12723,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 合肥万象城</t>
+          <t>成都仁和新城城市展厅109</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 合肥万象城</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12748,29 +12748,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 65%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅109</t>
+          <t>蔚来中心 | 合肥万象城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>蔚来空间 | 合肥万象城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 65%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -10914,7 +10914,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>东莞捷世丰</t>
+          <t>东莞世奥</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
+          <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>东莞世奥</t>
+          <t>东莞捷世丰</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市南城区莞太大道石鼓路段</t>
+          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
     </row>
@@ -10968,7 +10968,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>佛山世锦</t>
+          <t>佛山广物君奥</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
+          <t>广东省佛山市禅城区佛山大道中路83号</t>
         </is>
       </c>
     </row>
@@ -10995,7 +10995,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>佛山广物君奥</t>
+          <t>佛山世锦</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区佛山大道中路83号</t>
+          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
         </is>
       </c>
     </row>
@@ -11631,7 +11631,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>吉林省通化市东昌区新胜北路2459号</t>
+          <t>吉林省通化市新胜北路2459号</t>
         </is>
       </c>
     </row>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>吉林省通化市新胜北路2459号</t>
+          <t>吉林省通化市东昌区新胜北路2459号</t>
         </is>
       </c>
     </row>
@@ -11837,12 +11837,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11852,29 +11852,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11884,29 +11884,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11916,29 +11916,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
@@ -11987,22 +11987,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
@@ -12024,17 +12024,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
@@ -12056,17 +12056,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
@@ -12088,17 +12088,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
@@ -12120,17 +12120,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12140,29 +12140,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12172,29 +12172,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12236,29 +12236,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12280,17 +12280,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
         </is>
       </c>
     </row>
@@ -12312,17 +12312,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12332,29 +12332,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12364,29 +12364,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12408,17 +12408,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
         </is>
       </c>
     </row>
@@ -12440,17 +12440,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12460,29 +12460,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
         </is>
       </c>
     </row>
@@ -12504,17 +12504,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12524,29 +12524,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12556,29 +12556,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12588,29 +12588,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12659,22 +12659,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12691,22 +12691,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（29家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（32家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（32条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（29家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（32家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（32条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>东莞世奥</t>
+          <t>东莞捷世丰</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市南城区莞太大道石鼓路段</t>
+          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>东莞捷世丰</t>
+          <t>东莞世奥</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
+          <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
     </row>
@@ -10968,7 +10968,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>佛山广物君奥</t>
+          <t>佛山世锦</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区佛山大道中路83号</t>
+          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
         </is>
       </c>
     </row>
@@ -10995,7 +10995,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>佛山世锦</t>
+          <t>佛山广物君奥</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
+          <t>广东省佛山市禅城区佛山大道中路83号</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>广东广物金盈汽车贸易有限公司</t>
+          <t>广州南菱奥申</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区机场路898号</t>
+          <t>广东省广州市白云区广花一路136号</t>
         </is>
       </c>
     </row>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>广州南菱奥申</t>
+          <t>广东广物金盈汽车贸易有限公司</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广花一路136号</t>
+          <t>广东省广州市白云区机场路898号</t>
         </is>
       </c>
     </row>
@@ -11184,7 +11184,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>福建华奥</t>
+          <t>福建润通</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇良安路20号</t>
+          <t>福建省福州市仓山区高仕路2号</t>
         </is>
       </c>
     </row>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>福建润通</t>
+          <t>福建华奥</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区高仕路2号</t>
+          <t>福建省福州市闽侯县尚干镇良安路20号</t>
         </is>
       </c>
     </row>
@@ -11827,22 +11827,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11852,29 +11852,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -11901,12 +11901,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11916,29 +11916,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
+          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
@@ -11960,17 +11960,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -11992,17 +11992,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
@@ -12024,17 +12024,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
         </is>
       </c>
     </row>
@@ -12056,17 +12056,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12076,29 +12076,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12108,29 +12108,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12140,7 +12140,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -12152,17 +12152,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
@@ -12184,17 +12184,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12236,29 +12236,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12268,29 +12268,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12300,29 +12300,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
         </is>
       </c>
     </row>
@@ -12344,17 +12344,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12376,17 +12376,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12396,29 +12396,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -12440,17 +12440,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
         </is>
       </c>
     </row>
@@ -12472,17 +12472,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
+          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
         </is>
       </c>
     </row>
@@ -12531,22 +12531,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
@@ -12568,17 +12568,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12588,29 +12588,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
+          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12659,22 +12659,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12691,22 +12691,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（29家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（32家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（32条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（29家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（32家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（32条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆二郎销售中心</t>
+          <t>小鹏汽车重庆两江新区交付中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区石新路172号附2号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆两江新区交付中心</t>
+          <t>小鹏汽车重庆二郎销售中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>重庆市九龙坡区石新路172号附2号</t>
         </is>
       </c>
     </row>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>东莞捷世丰</t>
+          <t>东莞世奥</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
+          <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>东莞世奥</t>
+          <t>东莞捷世丰</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市南城区莞太大道石鼓路段</t>
+          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
     </row>
@@ -11631,7 +11631,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>吉林省通化市新胜北路2459号</t>
+          <t>吉林省通化市东昌区新胜北路2459号</t>
         </is>
       </c>
     </row>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>吉林省通化市东昌区新胜北路2459号</t>
+          <t>吉林省通化市新胜北路2459号</t>
         </is>
       </c>
     </row>
@@ -11827,22 +11827,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -11864,17 +11864,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11884,29 +11884,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11916,29 +11916,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11948,29 +11948,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
         </is>
       </c>
     </row>
@@ -11992,17 +11992,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
         </is>
       </c>
     </row>
@@ -12024,17 +12024,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
@@ -12056,17 +12056,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12076,29 +12076,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12108,29 +12108,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12140,29 +12140,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12172,14 +12172,14 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12204,29 +12204,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12248,17 +12248,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12268,29 +12268,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
         </is>
       </c>
     </row>
@@ -12312,17 +12312,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
+          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
         </is>
       </c>
     </row>
@@ -12344,17 +12344,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12376,17 +12376,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12408,17 +12408,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12440,17 +12440,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
+          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
         </is>
       </c>
     </row>
@@ -12472,17 +12472,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
@@ -12504,17 +12504,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
@@ -12568,17 +12568,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12588,29 +12588,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12627,22 +12627,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12659,22 +12659,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12696,17 +12696,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12723,22 +12723,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅109</t>
+          <t>蔚来中心 | 合肥万象城</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>蔚来空间 | 合肥万象城</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12748,29 +12748,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 65%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 合肥万象城</t>
+          <t>成都仁和新城城市展厅109</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 合肥万象城</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -12780,29 +12780,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 65%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>南昌红谷滩万象天地新能源空间</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
+          <t>南昌红谷滩印象城新能源空间</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -12812,29 +12812,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩万象天地新能源空间</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩印象城新能源空间</t>
+          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（29家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（32家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（32条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（29家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（32家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（32条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>东莞世奥</t>
+          <t>东莞捷世丰</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市南城区莞太大道石鼓路段</t>
+          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>东莞捷世丰</t>
+          <t>东莞世奥</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
+          <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>广州南菱奥申</t>
+          <t>广东广物金盈汽车贸易有限公司</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广花一路136号</t>
+          <t>广东省广州市白云区机场路898号</t>
         </is>
       </c>
     </row>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>广东广物金盈汽车贸易有限公司</t>
+          <t>广州南菱奥申</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区机场路898号</t>
+          <t>广东省广州市白云区广花一路136号</t>
         </is>
       </c>
     </row>
@@ -11827,22 +11827,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
@@ -11864,17 +11864,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11884,29 +11884,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11916,29 +11916,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11948,29 +11948,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
@@ -11992,17 +11992,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12012,29 +12012,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
+          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12056,17 +12056,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
         </is>
       </c>
     </row>
@@ -12088,17 +12088,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
+          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
         </is>
       </c>
     </row>
@@ -12120,17 +12120,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12140,7 +12140,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12152,17 +12152,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12172,29 +12172,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12204,29 +12204,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
         </is>
       </c>
     </row>
@@ -12248,17 +12248,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
@@ -12280,17 +12280,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12300,29 +12300,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12332,29 +12332,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12364,29 +12364,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12396,29 +12396,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
@@ -12440,17 +12440,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
+          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
         </is>
       </c>
     </row>
@@ -12472,17 +12472,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
         </is>
       </c>
     </row>
@@ -12504,17 +12504,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12524,29 +12524,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12556,29 +12556,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12627,22 +12627,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12659,22 +12659,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12691,22 +12691,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12723,22 +12723,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 合肥万象城</t>
+          <t>成都仁和新城城市展厅109</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 合肥万象城</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12748,29 +12748,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 65%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅109</t>
+          <t>蔚来中心 | 合肥万象城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>蔚来空间 | 合肥万象城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 65%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（29家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（32家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（32条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（29家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（32家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（32条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆两江新区交付中心</t>
+          <t>小鹏汽车重庆二郎销售中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>重庆市九龙坡区石新路172号附2号</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆二郎销售中心</t>
+          <t>小鹏汽车重庆两江新区交付中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区石新路172号附2号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>东莞捷世丰</t>
+          <t>东莞世奥</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
+          <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>东莞世奥</t>
+          <t>东莞捷世丰</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市南城区莞太大道石鼓路段</t>
+          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>广东广物金盈汽车贸易有限公司</t>
+          <t>广州南菱奥申</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区机场路898号</t>
+          <t>广东省广州市白云区广花一路136号</t>
         </is>
       </c>
     </row>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>广州南菱奥申</t>
+          <t>广东广物金盈汽车贸易有限公司</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广花一路136号</t>
+          <t>广东省广州市白云区机场路898号</t>
         </is>
       </c>
     </row>
@@ -11184,7 +11184,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>福建润通</t>
+          <t>福建华奥</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区高仕路2号</t>
+          <t>福建省福州市闽侯县尚干镇良安路20号</t>
         </is>
       </c>
     </row>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>福建华奥</t>
+          <t>福建润通</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇良安路20号</t>
+          <t>福建省福州市仓山区高仕路2号</t>
         </is>
       </c>
     </row>
@@ -11631,7 +11631,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>吉林省通化市东昌区新胜北路2459号</t>
+          <t>吉林省通化市新胜北路2459号</t>
         </is>
       </c>
     </row>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>吉林省通化市新胜北路2459号</t>
+          <t>吉林省通化市东昌区新胜北路2459号</t>
         </is>
       </c>
     </row>
@@ -11827,22 +11827,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -11864,17 +11864,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11896,17 +11896,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11916,29 +11916,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
+          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
         </is>
       </c>
     </row>
@@ -11960,17 +11960,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
@@ -11992,17 +11992,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12012,29 +12012,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
         </is>
       </c>
     </row>
@@ -12056,17 +12056,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
@@ -12088,17 +12088,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12108,29 +12108,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12140,29 +12140,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
@@ -12184,17 +12184,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12204,29 +12204,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -12248,17 +12248,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
         </is>
       </c>
     </row>
@@ -12280,17 +12280,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
@@ -12312,17 +12312,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12344,17 +12344,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
         </is>
       </c>
     </row>
@@ -12376,17 +12376,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12396,29 +12396,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12428,29 +12428,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12460,29 +12460,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12492,29 +12492,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12524,29 +12524,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12556,29 +12556,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
         </is>
       </c>
     </row>
@@ -12627,22 +12627,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12659,22 +12659,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12691,22 +12691,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12787,22 +12787,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩万象天地新能源空间</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩印象城新能源空间</t>
+          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -12812,29 +12812,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>南昌红谷滩万象天地新能源空间</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
+          <t>南昌红谷滩印象城新能源空间</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -10461,7 +10461,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆二郎销售中心</t>
+          <t>小鹏汽车重庆两江新区交付中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区石新路172号附2号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆两江新区交付中心</t>
+          <t>小鹏汽车重庆二郎销售中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>重庆市九龙坡区石新路172号附2号</t>
         </is>
       </c>
     </row>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>东莞世奥</t>
+          <t>东莞捷世丰</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市南城区莞太大道石鼓路段</t>
+          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>东莞捷世丰</t>
+          <t>东莞世奥</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
+          <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
     </row>
@@ -11184,7 +11184,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>福建华奥</t>
+          <t>福建润通</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇良安路20号</t>
+          <t>福建省福州市仓山区高仕路2号</t>
         </is>
       </c>
     </row>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>福建润通</t>
+          <t>福建华奥</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区高仕路2号</t>
+          <t>福建省福州市闽侯县尚干镇良安路20号</t>
         </is>
       </c>
     </row>
@@ -11631,7 +11631,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>吉林省通化市新胜北路2459号</t>
+          <t>吉林省通化市东昌区新胜北路2459号</t>
         </is>
       </c>
     </row>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>吉林省通化市东昌区新胜北路2459号</t>
+          <t>吉林省通化市新胜北路2459号</t>
         </is>
       </c>
     </row>
@@ -11827,22 +11827,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11852,29 +11852,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
         </is>
       </c>
     </row>
@@ -11896,17 +11896,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
+          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
         </is>
       </c>
     </row>
@@ -11928,17 +11928,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
@@ -11960,17 +11960,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11980,29 +11980,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12012,29 +12012,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12044,29 +12044,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12076,29 +12076,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12120,17 +12120,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12140,29 +12140,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12172,29 +12172,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12204,29 +12204,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12236,29 +12236,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12280,17 +12280,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12300,29 +12300,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12332,29 +12332,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12376,17 +12376,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
         </is>
       </c>
     </row>
@@ -12408,17 +12408,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12428,29 +12428,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12460,29 +12460,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
@@ -12504,17 +12504,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
@@ -12568,17 +12568,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12588,29 +12588,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12627,22 +12627,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12659,22 +12659,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12691,22 +12691,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8715</v>
+        <v>8717</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8712</v>
+        <v>8714</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-3</v>
@@ -897,7 +897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E434"/>
+  <dimension ref="A1:E436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6507,14 +6507,14 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C267" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D267" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E267" s="2" t="n">
         <v>0</v>
@@ -6528,14 +6528,14 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C268" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D268" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E268" s="2" t="n">
         <v>0</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C269" s="2" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C270" s="2" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C271" s="2" t="n">
@@ -6612,59 +6612,59 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D272" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D273" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="C272" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D272" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E272" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="3" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B273" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C273" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="D273" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="E273" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="3" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B274" s="3" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C274" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="D274" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="E274" s="3" t="n">
-        <v>-1</v>
+      <c r="C274" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D274" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -6675,14 +6675,14 @@
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C275" s="3" t="n">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="D275" s="3" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="E275" s="3" t="n">
         <v>-1</v>
@@ -6696,59 +6696,59 @@
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C276" s="3" t="n">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="D276" s="3" t="n">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="E276" s="3" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="inlineStr">
+      <c r="A277" s="3" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B277" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C277" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D277" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E277" s="2" t="n">
-        <v>0</v>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D277" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="E277" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="inlineStr">
+      <c r="A278" s="3" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B278" s="2" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C278" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D278" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E278" s="2" t="n">
-        <v>0</v>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D278" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E278" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="279">
@@ -6759,14 +6759,14 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C279" s="2" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D279" s="2" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E279" s="2" t="n">
         <v>0</v>
@@ -6780,14 +6780,14 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C280" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D280" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E280" s="2" t="n">
         <v>0</v>
@@ -6801,14 +6801,14 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C281" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D281" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E281" s="2" t="n">
         <v>0</v>
@@ -6822,14 +6822,14 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C282" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D282" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E282" s="2" t="n">
         <v>0</v>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C283" s="2" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D283" s="2" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E283" s="2" t="n">
         <v>0</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C284" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D284" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E284" s="2" t="n">
         <v>0</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C285" s="2" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D285" s="2" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="E285" s="2" t="n">
         <v>0</v>
@@ -6906,14 +6906,14 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C286" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D286" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E286" s="2" t="n">
         <v>0</v>
@@ -6927,14 +6927,14 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C287" s="2" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="D287" s="2" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E287" s="2" t="n">
         <v>0</v>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C288" s="2" t="n">
@@ -6969,14 +6969,14 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C289" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E289" s="2" t="n">
         <v>0</v>
@@ -6990,14 +6990,14 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C290" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D290" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E290" s="2" t="n">
         <v>0</v>
@@ -7011,14 +7011,14 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C291" s="2" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D291" s="2" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E291" s="2" t="n">
         <v>0</v>
@@ -7032,14 +7032,14 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C292" s="2" t="n">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="D292" s="2" t="n">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="E292" s="2" t="n">
         <v>0</v>
@@ -7053,14 +7053,14 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C293" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D293" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E293" s="2" t="n">
         <v>0</v>
@@ -7074,14 +7074,14 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C294" s="2" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="D294" s="2" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="E294" s="2" t="n">
         <v>0</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C295" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D295" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E295" s="2" t="n">
         <v>0</v>
@@ -7116,14 +7116,14 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C296" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D296" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E296" s="2" t="n">
         <v>0</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C297" s="2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D297" s="2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E297" s="2" t="n">
         <v>0</v>
@@ -7158,14 +7158,14 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C298" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D298" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E298" s="2" t="n">
         <v>0</v>
@@ -7179,14 +7179,14 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C299" s="2" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D299" s="2" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E299" s="2" t="n">
         <v>0</v>
@@ -7200,14 +7200,14 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C300" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D300" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E300" s="2" t="n">
         <v>0</v>
@@ -7221,14 +7221,14 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C301" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D301" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E301" s="2" t="n">
         <v>0</v>
@@ -7242,14 +7242,14 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C302" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D302" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E302" s="2" t="n">
         <v>0</v>
@@ -7258,19 +7258,19 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C303" s="2" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D303" s="2" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="E303" s="2" t="n">
         <v>0</v>
@@ -7279,19 +7279,19 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C304" s="2" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D304" s="2" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E304" s="2" t="n">
         <v>0</v>
@@ -7305,14 +7305,14 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C305" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D305" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E305" s="2" t="n">
         <v>0</v>
@@ -7326,14 +7326,14 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C306" s="2" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D306" s="2" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E306" s="2" t="n">
         <v>0</v>
@@ -7347,14 +7347,14 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C307" s="2" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D307" s="2" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E307" s="2" t="n">
         <v>0</v>
@@ -7368,14 +7368,14 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C308" s="2" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D308" s="2" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="E308" s="2" t="n">
         <v>0</v>
@@ -7389,14 +7389,14 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C309" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D309" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E309" s="2" t="n">
         <v>0</v>
@@ -7410,14 +7410,14 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C310" s="2" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="D310" s="2" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="E310" s="2" t="n">
         <v>0</v>
@@ -7431,14 +7431,14 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C311" s="2" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E311" s="2" t="n">
         <v>0</v>
@@ -7452,14 +7452,14 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C312" s="2" t="n">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="D312" s="2" t="n">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="E312" s="2" t="n">
         <v>0</v>
@@ -7473,14 +7473,14 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C313" s="2" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D313" s="2" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E313" s="2" t="n">
         <v>0</v>
@@ -7494,14 +7494,14 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C314" s="2" t="n">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="D314" s="2" t="n">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="E314" s="2" t="n">
         <v>0</v>
@@ -7515,14 +7515,14 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C315" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D315" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E315" s="2" t="n">
         <v>0</v>
@@ -7536,14 +7536,14 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C316" s="2" t="n">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="D316" s="2" t="n">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="E316" s="2" t="n">
         <v>0</v>
@@ -7557,14 +7557,14 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C317" s="2" t="n">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="D317" s="2" t="n">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="E317" s="2" t="n">
         <v>0</v>
@@ -7578,14 +7578,14 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C318" s="2" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D318" s="2" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E318" s="2" t="n">
         <v>0</v>
@@ -7599,14 +7599,14 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C319" s="2" t="n">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="D319" s="2" t="n">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="E319" s="2" t="n">
         <v>0</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C320" s="2" t="n">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D320" s="2" t="n">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="E320" s="2" t="n">
         <v>0</v>
@@ -7641,14 +7641,14 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C321" s="2" t="n">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="E321" s="2" t="n">
         <v>0</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C322" s="2" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="D322" s="2" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="E322" s="2" t="n">
         <v>0</v>
@@ -7683,14 +7683,14 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C323" s="2" t="n">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="D323" s="2" t="n">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="E323" s="2" t="n">
         <v>0</v>
@@ -7704,14 +7704,14 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C324" s="2" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D324" s="2" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E324" s="2" t="n">
         <v>0</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C325" s="2" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D325" s="2" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="E325" s="2" t="n">
         <v>0</v>
@@ -7746,14 +7746,14 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C326" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D326" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E326" s="2" t="n">
         <v>0</v>
@@ -7767,14 +7767,14 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C327" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D327" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E327" s="2" t="n">
         <v>0</v>
@@ -7788,14 +7788,14 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C328" s="2" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D328" s="2" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E328" s="2" t="n">
         <v>0</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C329" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D329" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E329" s="2" t="n">
         <v>0</v>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C330" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D330" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E330" s="2" t="n">
         <v>0</v>
@@ -7851,14 +7851,14 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C331" s="2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D331" s="2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E331" s="2" t="n">
         <v>0</v>
@@ -7872,14 +7872,14 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C332" s="2" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D332" s="2" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E332" s="2" t="n">
         <v>0</v>
@@ -7893,101 +7893,101 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D333" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E333" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D334" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E334" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C333" s="2" t="n">
+      <c r="C335" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D333" s="2" t="n">
+      <c r="D335" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="E333" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="3" t="inlineStr">
+      <c r="E335" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="3" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B334" s="3" t="inlineStr">
+      <c r="B336" s="3" t="inlineStr">
         <is>
           <t>广东</t>
         </is>
       </c>
-      <c r="C334" s="3" t="n">
+      <c r="C336" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="D334" s="3" t="n">
+      <c r="D336" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="E334" s="3" t="n">
+      <c r="E336" s="3" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="335">
-      <c r="A335" s="3" t="inlineStr">
+    <row r="337">
+      <c r="A337" s="3" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B335" s="3" t="inlineStr">
+      <c r="B337" s="3" t="inlineStr">
         <is>
           <t>河南</t>
         </is>
       </c>
-      <c r="C335" s="3" t="n">
+      <c r="C337" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="D335" s="3" t="n">
+      <c r="D337" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="E335" s="3" t="n">
+      <c r="E337" s="3" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="2" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B336" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C336" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D336" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E336" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="2" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B337" s="2" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C337" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D337" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E337" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -7998,14 +7998,14 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C338" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D338" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E338" s="2" t="n">
         <v>0</v>
@@ -8019,14 +8019,14 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C339" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D339" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E339" s="2" t="n">
         <v>0</v>
@@ -8040,14 +8040,14 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C340" s="2" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D340" s="2" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E340" s="2" t="n">
         <v>0</v>
@@ -8061,14 +8061,14 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C341" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D341" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E341" s="2" t="n">
         <v>0</v>
@@ -8082,14 +8082,14 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C342" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D342" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E342" s="2" t="n">
         <v>0</v>
@@ -8103,14 +8103,14 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C343" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D343" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E343" s="2" t="n">
         <v>0</v>
@@ -8124,14 +8124,14 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C344" s="2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D344" s="2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E344" s="2" t="n">
         <v>0</v>
@@ -8145,14 +8145,14 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C345" s="2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D345" s="2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E345" s="2" t="n">
         <v>0</v>
@@ -8166,14 +8166,14 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C346" s="2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D346" s="2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E346" s="2" t="n">
         <v>0</v>
@@ -8187,14 +8187,14 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C347" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D347" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E347" s="2" t="n">
         <v>0</v>
@@ -8208,14 +8208,14 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C348" s="2" t="n">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="D348" s="2" t="n">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="E348" s="2" t="n">
         <v>0</v>
@@ -8229,14 +8229,14 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C349" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D349" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E349" s="2" t="n">
         <v>0</v>
@@ -8250,14 +8250,14 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C350" s="2" t="n">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D350" s="2" t="n">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="E350" s="2" t="n">
         <v>0</v>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C351" s="2" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D351" s="2" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="E351" s="2" t="n">
         <v>0</v>
@@ -8292,14 +8292,14 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C352" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D352" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E352" s="2" t="n">
         <v>0</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C353" s="2" t="n">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="D353" s="2" t="n">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="E353" s="2" t="n">
         <v>0</v>
@@ -8334,14 +8334,14 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C354" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D354" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E354" s="2" t="n">
         <v>0</v>
@@ -8355,14 +8355,14 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C355" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D355" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E355" s="2" t="n">
         <v>0</v>
@@ -8376,14 +8376,14 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C356" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D356" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E356" s="2" t="n">
         <v>0</v>
@@ -8397,14 +8397,14 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C357" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D357" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E357" s="2" t="n">
         <v>0</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C358" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D358" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E358" s="2" t="n">
         <v>0</v>
@@ -8439,14 +8439,14 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C359" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D359" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E359" s="2" t="n">
         <v>0</v>
@@ -8460,14 +8460,14 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C360" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D360" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E360" s="2" t="n">
         <v>0</v>
@@ -8481,14 +8481,14 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C361" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D361" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E361" s="2" t="n">
         <v>0</v>
@@ -8502,49 +8502,49 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C362" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D362" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E362" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="4" t="inlineStr">
+      <c r="A363" s="2" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B363" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C363" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="D363" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="E363" s="4" t="n">
-        <v>1</v>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D363" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E363" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C364" s="2" t="n">
@@ -8558,24 +8558,24 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="2" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁</t>
-        </is>
-      </c>
-      <c r="B365" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C365" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D365" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E365" s="2" t="n">
-        <v>0</v>
+      <c r="A365" s="4" t="inlineStr">
+        <is>
+          <t>蔚来</t>
+        </is>
+      </c>
+      <c r="B365" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C365" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D365" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="E365" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="366">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C366" s="2" t="n">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C367" s="2" t="n">
@@ -8628,14 +8628,14 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C368" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D368" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E368" s="2" t="n">
         <v>0</v>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C369" s="2" t="n">
@@ -8670,14 +8670,14 @@
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C370" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D370" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E370" s="2" t="n">
         <v>0</v>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C371" s="2" t="n">
@@ -8712,14 +8712,14 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C372" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D372" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E372" s="2" t="n">
         <v>0</v>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C373" s="2" t="n">
@@ -8749,19 +8749,19 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C374" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D374" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E374" s="2" t="n">
         <v>0</v>
@@ -8770,19 +8770,19 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C375" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D375" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E375" s="2" t="n">
         <v>0</v>
@@ -8796,14 +8796,14 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C376" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D376" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E376" s="2" t="n">
         <v>0</v>
@@ -8817,14 +8817,14 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C377" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D377" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E377" s="2" t="n">
         <v>0</v>
@@ -8838,14 +8838,14 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C378" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D378" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E378" s="2" t="n">
         <v>0</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C379" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D379" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E379" s="2" t="n">
         <v>0</v>
@@ -8880,14 +8880,14 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C380" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D380" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E380" s="2" t="n">
         <v>0</v>
@@ -8901,14 +8901,14 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C381" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D381" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E381" s="2" t="n">
         <v>0</v>
@@ -8922,14 +8922,14 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C382" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D382" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E382" s="2" t="n">
         <v>0</v>
@@ -8943,14 +8943,14 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C383" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D383" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E383" s="2" t="n">
         <v>0</v>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C384" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D384" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E384" s="2" t="n">
         <v>0</v>
@@ -8985,14 +8985,14 @@
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C385" s="2" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="D385" s="2" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="E385" s="2" t="n">
         <v>0</v>
@@ -9006,14 +9006,14 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C386" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D386" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E386" s="2" t="n">
         <v>0</v>
@@ -9027,14 +9027,14 @@
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C387" s="2" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="D387" s="2" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="E387" s="2" t="n">
         <v>0</v>
@@ -9048,14 +9048,14 @@
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C388" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D388" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E388" s="2" t="n">
         <v>0</v>
@@ -9069,14 +9069,14 @@
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C389" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D389" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E389" s="2" t="n">
         <v>0</v>
@@ -9090,14 +9090,14 @@
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C390" s="2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D390" s="2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E390" s="2" t="n">
         <v>0</v>
@@ -9111,14 +9111,14 @@
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C391" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D391" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E391" s="2" t="n">
         <v>0</v>
@@ -9132,14 +9132,14 @@
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C392" s="2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D392" s="2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E392" s="2" t="n">
         <v>0</v>
@@ -9153,14 +9153,14 @@
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C393" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D393" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E393" s="2" t="n">
         <v>0</v>
@@ -9174,14 +9174,14 @@
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C394" s="2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D394" s="2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E394" s="2" t="n">
         <v>0</v>
@@ -9195,14 +9195,14 @@
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C395" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D395" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E395" s="2" t="n">
         <v>0</v>
@@ -9216,14 +9216,14 @@
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C396" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D396" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E396" s="2" t="n">
         <v>0</v>
@@ -9237,14 +9237,14 @@
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C397" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D397" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E397" s="2" t="n">
         <v>0</v>
@@ -9258,14 +9258,14 @@
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C398" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D398" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E398" s="2" t="n">
         <v>0</v>
@@ -9279,14 +9279,14 @@
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C399" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D399" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E399" s="2" t="n">
         <v>0</v>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C400" s="2" t="n">
@@ -9321,14 +9321,14 @@
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C401" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D401" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E401" s="2" t="n">
         <v>0</v>
@@ -9342,14 +9342,14 @@
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C402" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D402" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E402" s="2" t="n">
         <v>0</v>
@@ -9363,59 +9363,59 @@
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D403" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E403" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D404" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E404" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C403" s="2" t="n">
+      <c r="C405" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D403" s="2" t="n">
+      <c r="D405" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E403" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B404" s="3" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C404" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="D404" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="E404" s="3" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B405" s="3" t="inlineStr">
-        <is>
-          <t>吉林</t>
-        </is>
-      </c>
-      <c r="C405" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="D405" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="E405" s="3" t="n">
-        <v>-1</v>
+      <c r="E405" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -9426,59 +9426,59 @@
       </c>
       <c r="B406" s="3" t="inlineStr">
         <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C406" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="D406" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="E406" s="3" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B407" s="3" t="inlineStr">
+        <is>
+          <t>吉林</t>
+        </is>
+      </c>
+      <c r="C407" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D407" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="E407" s="3" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
           <t>甘肃</t>
         </is>
       </c>
-      <c r="C406" s="3" t="n">
+      <c r="C408" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D406" s="3" t="n">
+      <c r="D408" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E406" s="3" t="n">
+      <c r="E408" s="3" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B407" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C407" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="D407" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="E407" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B408" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C408" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="D408" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="E408" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="409">
@@ -9489,14 +9489,14 @@
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C409" s="2" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D409" s="2" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E409" s="2" t="n">
         <v>0</v>
@@ -9510,14 +9510,14 @@
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C410" s="2" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="D410" s="2" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="E410" s="2" t="n">
         <v>0</v>
@@ -9531,14 +9531,14 @@
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C411" s="2" t="n">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="D411" s="2" t="n">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="E411" s="2" t="n">
         <v>0</v>
@@ -9552,14 +9552,14 @@
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C412" s="2" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="D412" s="2" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="E412" s="2" t="n">
         <v>0</v>
@@ -9573,14 +9573,14 @@
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C413" s="2" t="n">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="D413" s="2" t="n">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="E413" s="2" t="n">
         <v>0</v>
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C414" s="2" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D414" s="2" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E414" s="2" t="n">
         <v>0</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C415" s="2" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D415" s="2" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E415" s="2" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C416" s="2" t="n">
-        <v>145</v>
+        <v>35</v>
       </c>
       <c r="D416" s="2" t="n">
-        <v>145</v>
+        <v>35</v>
       </c>
       <c r="E416" s="2" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C417" s="2" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D417" s="2" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E417" s="2" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C418" s="2" t="n">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="D418" s="2" t="n">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="E418" s="2" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C419" s="2" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D419" s="2" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E419" s="2" t="n">
         <v>0</v>
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C420" s="2" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D420" s="2" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E420" s="2" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C421" s="2" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="D421" s="2" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="E421" s="2" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C422" s="2" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D422" s="2" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E422" s="2" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C423" s="2" t="n">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="D423" s="2" t="n">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="E423" s="2" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C424" s="2" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="D424" s="2" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="E424" s="2" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C425" s="2" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="D425" s="2" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E425" s="2" t="n">
         <v>0</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C426" s="2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D426" s="2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E426" s="2" t="n">
         <v>0</v>
@@ -9867,59 +9867,59 @@
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D427" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E427" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="D428" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="E428" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
           <t>青海</t>
         </is>
       </c>
-      <c r="C427" s="2" t="n">
+      <c r="C429" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D427" s="2" t="n">
+      <c r="D429" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E427" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B428" s="4" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C428" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="D428" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="E428" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B429" s="4" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="C429" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="D429" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="E429" s="4" t="n">
-        <v>1</v>
+      <c r="E429" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="430">
@@ -9930,14 +9930,14 @@
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C430" s="4" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="D430" s="4" t="n">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="E430" s="4" t="n">
         <v>1</v>
@@ -9951,14 +9951,14 @@
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C431" s="4" t="n">
-        <v>150</v>
+        <v>42</v>
       </c>
       <c r="D431" s="4" t="n">
-        <v>151</v>
+        <v>43</v>
       </c>
       <c r="E431" s="4" t="n">
         <v>1</v>
@@ -9972,14 +9972,14 @@
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C432" s="4" t="n">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D432" s="4" t="n">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="E432" s="4" t="n">
         <v>1</v>
@@ -9993,14 +9993,14 @@
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C433" s="4" t="n">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="D433" s="4" t="n">
-        <v>22</v>
+        <v>151</v>
       </c>
       <c r="E433" s="4" t="n">
         <v>1</v>
@@ -10014,16 +10014,58 @@
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C434" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="D434" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E434" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B435" s="4" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="C435" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="D435" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="E435" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B436" s="4" t="inlineStr">
+        <is>
           <t>广东</t>
         </is>
       </c>
-      <c r="C434" s="4" t="n">
+      <c r="C436" s="4" t="n">
         <v>204</v>
       </c>
-      <c r="D434" s="4" t="n">
+      <c r="D436" s="4" t="n">
         <v>206</v>
       </c>
-      <c r="E434" s="4" t="n">
+      <c r="E436" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10461,7 +10503,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆两江新区交付中心</t>
+          <t>小鹏汽车重庆二郎销售中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -10476,7 +10518,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>重庆市九龙坡区石新路172号附2号</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10530,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆二郎销售中心</t>
+          <t>小鹏汽车重庆两江新区交付中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -10503,7 +10545,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区石新路172号附2号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -10914,7 +10956,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>东莞捷世丰</t>
+          <t>东莞世奥</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10929,7 +10971,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
+          <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10983,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>东莞世奥</t>
+          <t>东莞捷世丰</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -10956,7 +10998,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市南城区莞太大道石鼓路段</t>
+          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
     </row>
@@ -11832,17 +11874,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11852,7 +11894,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
         </is>
       </c>
     </row>
@@ -11869,12 +11911,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11884,29 +11926,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
+          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11916,7 +11958,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -11928,17 +11970,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11948,7 +11990,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
@@ -11987,22 +12029,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12012,29 +12054,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12044,7 +12086,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
@@ -12056,17 +12098,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12076,29 +12118,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12108,29 +12150,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12140,7 +12182,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12152,17 +12194,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12172,29 +12214,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12204,14 +12246,14 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -12221,12 +12263,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12236,7 +12278,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -12248,17 +12290,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12268,7 +12310,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
@@ -12280,17 +12322,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12300,7 +12342,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
@@ -12317,12 +12359,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12332,29 +12374,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12364,7 +12406,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
@@ -12376,17 +12418,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12396,29 +12438,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12428,14 +12470,14 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -12445,12 +12487,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12460,29 +12502,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12492,29 +12534,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12524,7 +12566,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
@@ -12536,17 +12578,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12556,7 +12598,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
         </is>
       </c>
     </row>
@@ -12568,17 +12610,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12588,7 +12630,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
+          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
         </is>
       </c>
     </row>
@@ -12627,22 +12669,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12691,22 +12733,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12723,22 +12765,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅109</t>
+          <t>蔚来中心 | 合肥万象城</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>蔚来空间 | 合肥万象城</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12748,29 +12790,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 65%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 合肥万象城</t>
+          <t>成都仁和新城城市展厅109</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 合肥万象城</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -12780,7 +12822,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 65%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（29家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（32家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（32条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（29家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（32家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（32条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>广州南菱奥申</t>
+          <t>广东广物金盈汽车贸易有限公司</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广花一路136号</t>
+          <t>广东省广州市白云区机场路898号</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>广东广物金盈汽车贸易有限公司</t>
+          <t>广州南菱奥申</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区机场路898号</t>
+          <t>广东省广州市白云区广花一路136号</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>福建润通</t>
+          <t>福建华奥</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区高仕路2号</t>
+          <t>福建省福州市闽侯县尚干镇良安路20号</t>
         </is>
       </c>
     </row>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>福建华奥</t>
+          <t>福建润通</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇良安路20号</t>
+          <t>福建省福州市仓山区高仕路2号</t>
         </is>
       </c>
     </row>
@@ -11869,7 +11869,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11894,29 +11894,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11926,29 +11926,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
@@ -11975,12 +11975,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11990,29 +11990,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12022,29 +12022,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12066,17 +12066,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12086,29 +12086,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12118,29 +12118,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12150,7 +12150,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12162,17 +12162,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12182,29 +12182,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
@@ -12226,17 +12226,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12246,29 +12246,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12278,29 +12278,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
         </is>
       </c>
     </row>
@@ -12322,17 +12322,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
@@ -12359,12 +12359,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12374,29 +12374,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12445,22 +12445,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12470,7 +12470,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
@@ -12482,17 +12482,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12502,29 +12502,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
         </is>
       </c>
     </row>
@@ -12546,17 +12546,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12566,29 +12566,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
@@ -12610,17 +12610,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
+          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
         </is>
       </c>
     </row>
@@ -12669,22 +12669,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12706,17 +12706,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12733,22 +12733,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12765,22 +12765,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 合肥万象城</t>
+          <t>成都仁和新城城市展厅109</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 合肥万象城</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12790,29 +12790,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 65%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅109</t>
+          <t>蔚来中心 | 合肥万象城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>蔚来空间 | 合肥万象城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -12822,29 +12822,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 65%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>南昌红谷滩万象天地新能源空间</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
+          <t>南昌红谷滩印象城新能源空间</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -12854,29 +12854,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩万象天地新能源空间</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩印象城新能源空间</t>
+          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -10956,7 +10956,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>东莞世奥</t>
+          <t>东莞捷世丰</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市南城区莞太大道石鼓路段</t>
+          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
     </row>
@@ -10983,7 +10983,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>东莞捷世丰</t>
+          <t>东莞世奥</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
+          <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>佛山世锦</t>
+          <t>佛山广物君奥</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
+          <t>广东省佛山市禅城区佛山大道中路83号</t>
         </is>
       </c>
     </row>
@@ -11037,7 +11037,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>佛山广物君奥</t>
+          <t>佛山世锦</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区佛山大道中路83号</t>
+          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>广东广物金盈汽车贸易有限公司</t>
+          <t>广州南菱奥申</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区机场路898号</t>
+          <t>广东省广州市白云区广花一路136号</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>广州南菱奥申</t>
+          <t>广东广物金盈汽车贸易有限公司</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广花一路136号</t>
+          <t>广东省广州市白云区机场路898号</t>
         </is>
       </c>
     </row>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>吉林省通化市东昌区新胜北路2459号</t>
+          <t>吉林省通化市新胜北路2459号</t>
         </is>
       </c>
     </row>
@@ -11700,7 +11700,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>吉林省通化市新胜北路2459号</t>
+          <t>吉林省通化市东昌区新胜北路2459号</t>
         </is>
       </c>
     </row>
@@ -11869,22 +11869,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11894,29 +11894,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11926,29 +11926,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -11970,17 +11970,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11990,29 +11990,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12022,7 +12022,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -12034,17 +12034,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12054,14 +12054,14 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12086,14 +12086,14 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -12103,12 +12103,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12118,29 +12118,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12150,29 +12150,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
         </is>
       </c>
     </row>
@@ -12194,17 +12194,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12214,29 +12214,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
         </is>
       </c>
     </row>
@@ -12263,12 +12263,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12278,7 +12278,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
@@ -12290,17 +12290,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
@@ -12327,12 +12327,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12342,29 +12342,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12374,29 +12374,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12406,29 +12406,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12438,29 +12438,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12470,7 +12470,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
         </is>
       </c>
     </row>
@@ -12482,17 +12482,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12502,29 +12502,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
@@ -12546,17 +12546,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12566,29 +12566,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -12610,17 +12610,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12630,29 +12630,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12669,22 +12669,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12701,22 +12701,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12733,22 +12733,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12765,22 +12765,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅109</t>
+          <t>蔚来中心 | 合肥万象城</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>蔚来空间 | 合肥万象城</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12790,29 +12790,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 65%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 合肥万象城</t>
+          <t>成都仁和新城城市展厅109</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 合肥万象城</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 65%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（29家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（32家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（32条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（29家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（33家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（31条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -788,17 +788,17 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>533</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
     </row>
@@ -872,13 +872,13 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8717</v>
+        <v>8718</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>8714</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
@@ -7956,14 +7956,14 @@
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C336" s="3" t="n">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="D336" s="3" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="E336" s="3" t="n">
         <v>-1</v>
@@ -7977,38 +7977,38 @@
       </c>
       <c r="B337" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C337" s="3" t="n">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="D337" s="3" t="n">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="E337" s="3" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="inlineStr">
+      <c r="A338" s="3" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B338" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C338" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D338" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E338" s="2" t="n">
-        <v>0</v>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="C338" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D338" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E338" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="339">
@@ -8019,14 +8019,14 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C339" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D339" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E339" s="2" t="n">
         <v>0</v>
@@ -8040,14 +8040,14 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C340" s="2" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D340" s="2" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E340" s="2" t="n">
         <v>0</v>
@@ -8061,14 +8061,14 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C341" s="2" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D341" s="2" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E341" s="2" t="n">
         <v>0</v>
@@ -8082,14 +8082,14 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C342" s="2" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D342" s="2" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="E342" s="2" t="n">
         <v>0</v>
@@ -8103,14 +8103,14 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C343" s="2" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D343" s="2" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E343" s="2" t="n">
         <v>0</v>
@@ -8124,14 +8124,14 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C344" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D344" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E344" s="2" t="n">
         <v>0</v>
@@ -8145,14 +8145,14 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C345" s="2" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D345" s="2" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E345" s="2" t="n">
         <v>0</v>
@@ -10080,7 +10080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10088,6 +10088,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10116,6 +10117,11 @@
           <t>地址</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>历史状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -10143,6 +10149,11 @@
           <t>北京市⼤兴区⾦时⼤街7号</t>
         </is>
       </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -10170,6 +10181,11 @@
           <t>湖北省黄石市开铁区大棋大道357号</t>
         </is>
       </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -10197,6 +10213,11 @@
           <t>淮南爱琴海购物中心</t>
         </is>
       </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260615~20260615，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -10224,6 +10245,11 @@
           <t>安徽省黄山市屯溪区高新技术产业开发区翰林路16号</t>
         </is>
       </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -10251,6 +10277,11 @@
           <t>山东省聊城市东昌府区柳园北路39号万达广场1楼</t>
         </is>
       </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -10278,6 +10309,11 @@
           <t>江西省南昌市红谷滩区九龙大道666号湾悦天地1号门中庭</t>
         </is>
       </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -10305,6 +10341,11 @@
           <t>广阳万达广场2号门</t>
         </is>
       </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -10332,6 +10373,11 @@
           <t>龙游县龙洲街道兴龙南路45号</t>
         </is>
       </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -10359,6 +10405,11 @@
           <t>歌山路7号</t>
         </is>
       </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -10386,6 +10437,11 @@
           <t>湖南省张家界市永定区解放路中商广场1F中庭</t>
         </is>
       </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -10413,6 +10469,11 @@
           <t>上海市浦东南路877、879、889、897号第1层101+102+103单元</t>
         </is>
       </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -10440,6 +10501,11 @@
           <t>济南市市中区英雄山路165号</t>
         </is>
       </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -10467,6 +10533,11 @@
           <t>昆山市开发区清江路38号2号房</t>
         </is>
       </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -10494,6 +10565,11 @@
           <t>湖州市吴兴区龙溪街道开发区彩凤路666号正洪产业园</t>
         </is>
       </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -10503,7 +10579,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆二郎销售中心</t>
+          <t>小鹏汽车重庆两江新区交付中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -10518,7 +10594,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区石新路172号附2号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10611,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆两江新区交付中心</t>
+          <t>小鹏汽车重庆二郎销售中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -10545,7 +10626,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>重庆市九龙坡区石新路172号附2号</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10575,6 +10661,11 @@
           <t>江西省赣州市兴国县兴国大道477号（兴国世茂翡翠城内）</t>
         </is>
       </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -10602,6 +10693,11 @@
           <t>陕西省宝鸡市渭滨区宝鸡市渭滨区高新大道48号</t>
         </is>
       </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -10629,6 +10725,11 @@
           <t>上海市浦东新区张杨北路1188号G层G-01</t>
         </is>
       </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -10656,6 +10757,11 @@
           <t>吉林省长春市南关区盛华大街277号</t>
         </is>
       </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -10683,6 +10789,11 @@
           <t>山东省青岛市黄岛区滨海大道2777号融创茂西门华为智能生活馆</t>
         </is>
       </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -10710,6 +10821,11 @@
           <t>山西省大同市平城区太和路与重熙街交叉口东北角百盛奥特莱斯1F</t>
         </is>
       </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -10737,6 +10853,11 @@
           <t>广东省中山市小榄镇坦背村坦背东二马路168号</t>
         </is>
       </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -10764,6 +10885,11 @@
           <t>广东省广州市天河区天河路228号正佳广场四楼4D169铺</t>
         </is>
       </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -10791,6 +10917,11 @@
           <t>河南省郑州市中原区建设西路郑州汇升汽车产业园</t>
         </is>
       </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -10818,6 +10949,11 @@
           <t>浙江省杭州市钱塘区下沙街道德胜东路2399号3号楼1层03号</t>
         </is>
       </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -10845,6 +10981,11 @@
           <t>贵州省安顺市西秀区新安街道产业园区大道1.5公里处</t>
         </is>
       </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -10872,6 +11013,11 @@
           <t>陕西省西安市长安区航天基地神舟八路225号</t>
         </is>
       </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -10897,6 +11043,11 @@
       <c r="E30" s="4" t="inlineStr">
         <is>
           <t>黑龙江省牡丹江市阳明区兴业路78号</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10911,7 +11062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10919,6 +11070,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10947,6 +11099,11 @@
           <t>地址</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>历史状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -10974,6 +11131,11 @@
           <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -11001,6 +11163,11 @@
           <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -11010,7 +11177,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>佛山广物君奥</t>
+          <t>佛山世锦</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -11025,7 +11192,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区佛山大道中路83号</t>
+          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
         </is>
       </c>
     </row>
@@ -11037,7 +11209,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>佛山世锦</t>
+          <t>佛山广物君奥</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -11052,7 +11224,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
+          <t>广东省佛山市禅城区佛山大道中路83号</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11241,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>广州南菱奥申</t>
+          <t>广东广物金盈汽车贸易有限公司</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -11079,7 +11256,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广花一路136号</t>
+          <t>广东省广州市白云区机场路898号</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11273,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>广东广物金盈汽车贸易有限公司</t>
+          <t>广州南菱奥申</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11106,7 +11288,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区机场路898号</t>
+          <t>广东省广州市白云区广花一路136号</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
         </is>
       </c>
     </row>
@@ -11136,6 +11323,11 @@
           <t>广东省惠州市惠城区三栋镇惠南汽车城2号</t>
         </is>
       </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -11163,6 +11355,11 @@
           <t>广东省汕头市龙湖区珠江路52号</t>
         </is>
       </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -11190,6 +11387,11 @@
           <t>广东省珠海市香洲区珠海大道屏东一路2号</t>
         </is>
       </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -11217,6 +11419,11 @@
           <t>湖南省湘潭市雨湖区白石路5号</t>
         </is>
       </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -11244,6 +11451,11 @@
           <t>福建省福州市闽侯县尚干镇良安路20号</t>
         </is>
       </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -11271,6 +11483,11 @@
           <t>福建省福州市仓山区高仕路2号</t>
         </is>
       </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -11298,6 +11515,11 @@
           <t>北京市大兴区大兴龙湖天街一层中庭</t>
         </is>
       </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -11325,6 +11547,11 @@
           <t>河北省廊坊市三河市燕郊开发区102国道27号燕郊永旺梦乐城一楼中庭</t>
         </is>
       </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -11352,6 +11579,11 @@
           <t>浙江省嘉兴市嘉善县嘉善大道399号嘉善银泰1楼L1-115蔚来门口</t>
         </is>
       </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -11379,6 +11611,11 @@
           <t>留下街道西溪路882号</t>
         </is>
       </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -11406,6 +11643,11 @@
           <t>爱情海购物中心18号3幢</t>
         </is>
       </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -11433,6 +11675,11 @@
           <t>河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -11460,6 +11707,11 @@
           <t>江苏省苏州市相城区人民路4555号</t>
         </is>
       </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -11487,6 +11739,11 @@
           <t>江西省赣州市龙南市龙南镇龙翔大道1号门</t>
         </is>
       </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 1 期</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -11514,6 +11771,11 @@
           <t>上海市闵行区莲花路1308号3幢107、108、109室 九龙湖国际企业园B2栋</t>
         </is>
       </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -11541,6 +11803,11 @@
           <t>广东省茂名市茂南区油城十路1号大院首层223-1号</t>
         </is>
       </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -11568,6 +11835,11 @@
           <t>江苏省苏州市高新区塔园路181号</t>
         </is>
       </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -11595,6 +11867,11 @@
           <t>陕西省西安市高新区普新二路9号普洛斯高新产业园B1特斯拉交付中心</t>
         </is>
       </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -11604,22 +11881,27 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州新塘永旺</t>
+          <t>蔚来中心 | 合肥万象城</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>广州市</t>
+          <t>合肥市</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市永旺梦乐城新塘购物中心1层1076区位</t>
+          <t>合肥蜀山区潜山路111号华润万象城L141蔚来汽车</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
         </is>
       </c>
     </row>
@@ -11631,49 +11913,59 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 郑东万象城</t>
+          <t>蔚来空间 | 广州新塘永旺</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>广州市</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>河南省郑州市金水区金水东路与东风南路交叉口西南角一层L148号</t>
+          <t>广东省广州市永旺梦乐城新塘购物中心1层1076区位</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•通化新胜北路</t>
+          <t>蔚来空间 | 郑东万象城</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>通化市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>吉林省通化市新胜北路2459号</t>
+          <t>河南省郑州市金水区金水东路与东风南路交叉口西南角一层L148号</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
         </is>
       </c>
     </row>
@@ -11703,6 +11995,11 @@
           <t>吉林省通化市东昌区新胜北路2459号</t>
         </is>
       </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -11712,22 +12009,27 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>鸿蒙智行授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>宿州市</t>
+          <t>通化市</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>吉林省通化市新胜北路2459号</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
         </is>
       </c>
     </row>
@@ -11739,7 +12041,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•淮北寇湾汽车城</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -11749,12 +12051,17 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>淮北市</t>
+          <t>宿州市</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>安徽省淮北市相山区任圩街道寇湾汽车城骏驰路3号201室</t>
+          <t>安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
         </is>
       </c>
     </row>
@@ -11766,22 +12073,27 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•兰州南滨河中路</t>
+          <t>鸿蒙智行尚界用户中心•淮北寇湾汽车城</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>兰州市</t>
+          <t>淮北市</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>甘肃省兰州市七里河区南滨河中路上河苑409号</t>
+          <t>安徽省淮北市相山区任圩街道寇湾汽车城骏驰路3号201室</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
         </is>
       </c>
     </row>
@@ -11793,22 +12105,59 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
+          <t>AITO授权用户中心•兰州南滨河中路</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>甘肃</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>兰州市</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>甘肃省兰州市七里河区南滨河中路上河苑409号</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
           <t>华为授权体验店（未来方舟）</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>贵州</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>贵阳市</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>贵州省贵阳市云岩区未来方舟G6组团一号电梯旁华为授权体验店</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
         </is>
       </c>
     </row>
@@ -11823,7 +12172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11874,17 +12223,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11894,7 +12243,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
@@ -11906,17 +12255,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11926,29 +12275,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11958,7 +12307,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
         </is>
       </c>
     </row>
@@ -11975,12 +12324,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11990,7 +12339,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
+          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
         </is>
       </c>
     </row>
@@ -12002,17 +12351,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12022,7 +12371,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12034,17 +12383,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12054,29 +12403,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12086,29 +12435,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12118,7 +12467,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
@@ -12130,17 +12479,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12150,7 +12499,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
@@ -12162,17 +12511,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12182,7 +12531,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
@@ -12194,17 +12543,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12214,29 +12563,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12246,29 +12595,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12278,29 +12627,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12310,7 +12659,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12322,17 +12671,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12342,29 +12691,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12374,7 +12723,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
         </is>
       </c>
     </row>
@@ -12386,17 +12735,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12406,7 +12755,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
         </is>
       </c>
     </row>
@@ -12418,17 +12767,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12438,29 +12787,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12470,7 +12819,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -12482,17 +12831,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12502,29 +12851,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12534,29 +12883,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12566,29 +12915,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12598,29 +12947,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12630,7 +12979,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12642,17 +12991,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12669,22 +13018,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12733,22 +13082,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12765,22 +13114,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 合肥万象城</t>
+          <t>成都仁和新城城市展厅109</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 合肥万象城</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12790,39 +13139,39 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 65%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅109</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
@@ -12855,38 +13204,6 @@
       <c r="F32" s="5" t="inlineStr">
         <is>
           <t>店名相似度 81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -10579,7 +10579,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆两江新区交付中心</t>
+          <t>小鹏汽车重庆二郎销售中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>重庆市九龙坡区石新路172号附2号</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆二郎销售中心</t>
+          <t>小鹏汽车重庆两江新区交付中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区石新路172号附2号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11070,7 +11070,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>东莞捷世丰</t>
+          <t>东莞世奥</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
+          <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>东莞世奥</t>
+          <t>东莞捷世丰</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市南城区莞太大道石鼓路段</t>
+          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>佛山世锦</t>
+          <t>佛山广物君奥</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
+          <t>广东省佛山市禅城区佛山大道中路83号</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>佛山广物君奥</t>
+          <t>佛山世锦</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区佛山大道中路83号</t>
+          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>福建华奥</t>
+          <t>福建润通</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇良安路20号</t>
+          <t>福建省福州市仓山区高仕路2号</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>福建润通</t>
+          <t>福建华奥</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区高仕路2号</t>
+          <t>福建省福州市闽侯县尚干镇良安路20号</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 2 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>连续在档 8 期</t>
+          <t>连续在档 8 期；本期存在高相似店名「小鹏汽车衡水昌明大街销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>连续在档 8 期</t>
+          <t>连续在档 8 期；本期存在高相似店名「AITO授权用户中心•通化新胜北路」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>连续在档 8 期</t>
+          <t>连续在档 8 期；本期存在高相似店名「AITO授权用户中心•通化新胜北路」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12223,17 +12223,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>华为智能生活馆•昆明南亚风情第壹城</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12243,29 +12243,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -12292,12 +12292,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12307,29 +12307,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
+          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12339,14 +12339,14 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
         </is>
       </c>
     </row>
@@ -12383,17 +12383,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12403,7 +12403,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12415,17 +12415,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12435,29 +12435,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
+          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -12484,12 +12484,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
+          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
         </is>
       </c>
     </row>
@@ -12511,17 +12511,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•保定朝阳北大街</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
+          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
         </is>
       </c>
     </row>
@@ -12543,17 +12543,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12563,29 +12563,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12595,29 +12595,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>AITO授权用户中心•湘潭九华</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
         </is>
       </c>
     </row>
@@ -12639,17 +12639,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12659,29 +12659,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
@@ -12703,17 +12703,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12723,29 +12723,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
+          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12794,22 +12794,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12819,29 +12819,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12851,29 +12851,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12883,29 +12883,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
         </is>
       </c>
     </row>
@@ -12927,17 +12927,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12947,29 +12947,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12979,29 +12979,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13018,22 +13018,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13050,22 +13050,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13082,22 +13082,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -9,9 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（29家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（33家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（31条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（24家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（31家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（16条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -851,17 +851,17 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1717</v>
+        <v>1451</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1721</v>
+        <v>1452</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8718</v>
+        <v>8452</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8714</v>
+        <v>8445</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
     </row>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="C406" s="3" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D406" s="3" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E406" s="3" t="n">
         <v>-2</v>
@@ -9447,14 +9447,14 @@
       </c>
       <c r="B407" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C407" s="3" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D407" s="3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E407" s="3" t="n">
         <v>-1</v>
@@ -9468,14 +9468,14 @@
       </c>
       <c r="B408" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C408" s="3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D408" s="3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E408" s="3" t="n">
         <v>-1</v>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="C409" s="2" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D409" s="2" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E409" s="2" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="C410" s="2" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D410" s="2" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E410" s="2" t="n">
         <v>0</v>
@@ -9535,10 +9535,10 @@
         </is>
       </c>
       <c r="C411" s="2" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D411" s="2" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E411" s="2" t="n">
         <v>0</v>
@@ -9556,10 +9556,10 @@
         </is>
       </c>
       <c r="C412" s="2" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D412" s="2" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E412" s="2" t="n">
         <v>0</v>
@@ -9573,14 +9573,14 @@
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C413" s="2" t="n">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="D413" s="2" t="n">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="E413" s="2" t="n">
         <v>0</v>
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C414" s="2" t="n">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="D414" s="2" t="n">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="E414" s="2" t="n">
         <v>0</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C415" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D415" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E415" s="2" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C416" s="2" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D416" s="2" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E416" s="2" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C417" s="2" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D417" s="2" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E417" s="2" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C418" s="2" t="n">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="D418" s="2" t="n">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="E418" s="2" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C419" s="2" t="n">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="D419" s="2" t="n">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="E419" s="2" t="n">
         <v>0</v>
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C420" s="2" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D420" s="2" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="E420" s="2" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C421" s="2" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D421" s="2" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="E421" s="2" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C422" s="2" t="n">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="D422" s="2" t="n">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="E422" s="2" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C423" s="2" t="n">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="D423" s="2" t="n">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="E423" s="2" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C424" s="2" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D424" s="2" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="E424" s="2" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C425" s="2" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D425" s="2" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="E425" s="2" t="n">
         <v>0</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C426" s="2" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D426" s="2" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E426" s="2" t="n">
         <v>0</v>
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C427" s="2" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="D427" s="2" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E427" s="2" t="n">
         <v>0</v>
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C428" s="2" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D428" s="2" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E428" s="2" t="n">
         <v>0</v>
@@ -9909,59 +9909,59 @@
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D429" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="E429" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D430" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="E430" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
           <t>青海</t>
         </is>
       </c>
-      <c r="C429" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D429" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E429" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B430" s="4" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C430" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="D430" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="E430" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B431" s="4" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="C431" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="D431" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="E431" s="4" t="n">
-        <v>1</v>
+      <c r="C431" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D431" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E431" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="432">
@@ -9972,14 +9972,14 @@
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C432" s="4" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D432" s="4" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E432" s="4" t="n">
         <v>1</v>
@@ -9993,14 +9993,14 @@
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C433" s="4" t="n">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="D433" s="4" t="n">
-        <v>151</v>
+        <v>37</v>
       </c>
       <c r="E433" s="4" t="n">
         <v>1</v>
@@ -10014,14 +10014,14 @@
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C434" s="4" t="n">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="D434" s="4" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="E434" s="4" t="n">
         <v>1</v>
@@ -10035,14 +10035,14 @@
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C435" s="4" t="n">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="D435" s="4" t="n">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="E435" s="4" t="n">
         <v>1</v>
@@ -10056,17 +10056,17 @@
       </c>
       <c r="B436" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C436" s="4" t="n">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="D436" s="4" t="n">
-        <v>206</v>
+        <v>19</v>
       </c>
       <c r="E436" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -10080,7 +10080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10739,27 +10739,27 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>华为智能生活馆•青岛融创茂</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>长春市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区盛华大街277号</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂西门华为智能生活馆</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10771,22 +10771,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛融创茂</t>
+          <t>华为授权体验店（百盛奥特莱斯）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>青岛市</t>
+          <t>大同市</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂西门华为智能生活馆</t>
+          <t>山西省大同市平城区太和路与重熙街交叉口东北角百盛奥特莱斯1F</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10803,22 +10803,22 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（百盛奥特莱斯）</t>
+          <t>华为授权体验店（正佳广场四楼）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>大同市</t>
+          <t>广州市</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>山西省大同市平城区太和路与重熙街交叉口东北角百盛奥特莱斯1F</t>
+          <t>广东省广州市天河区天河路228号正佳广场四楼4D169铺</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -10835,22 +10835,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•中山西区坦背</t>
+          <t>AITO授权用户中心•郑州建设路</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>中山市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>广东省中山市小榄镇坦背村坦背东二马路168号</t>
+          <t>河南省郑州市中原区建设西路郑州汇升汽车产业园</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -10867,185 +10867,25 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（正佳广场四楼）</t>
+          <t>鸿蒙智行尚界用户中心•牡丹江兴业路</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>广州市</t>
+          <t>牡丹江市</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市天河区天河路228号正佳广场四楼4D169铺</t>
+          <t>黑龙江省牡丹江市阳明区兴业路78号</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•郑州建设路</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>郑州市</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>河南省郑州市中原区建设西路郑州汇升汽车产业园</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•杭州梦马汽车小镇</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>杭州市</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号3号楼1层03号</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•安顺东冠汽车城</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>安顺市</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>贵州省安顺市西秀区新安街道产业园区大道1.5公里处</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•西安航天城</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>西安市</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>陕西省西安市长安区航天基地神舟八路225号</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260615，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•牡丹江兴业路</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>黑龙江</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>牡丹江市</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>黑龙江省牡丹江市阳明区兴业路78号</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
         </is>
@@ -11062,7 +10902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11177,7 +11017,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>佛山广物君奥</t>
+          <t>佛山世锦</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -11192,7 +11032,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区佛山大道中路83号</t>
+          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -11209,7 +11049,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>佛山世锦</t>
+          <t>佛山广物君奥</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -11224,7 +11064,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
+          <t>广东省佛山市禅城区佛山大道中路83号</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -11241,7 +11081,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>广东广物金盈汽车贸易有限公司</t>
+          <t>广州南菱奥申</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -11256,7 +11096,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区机场路898号</t>
+          <t>广东省广州市白云区广花一路136号</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -11273,7 +11113,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>广州南菱奥申</t>
+          <t>广东广物金盈汽车贸易有限公司</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11288,7 +11128,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广花一路136号</t>
+          <t>广东省广州市白云区机场路898号</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -11977,27 +11817,27 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•通化新胜北路</t>
+          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>通化市</t>
+          <t>宿州市</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>吉林省通化市东昌区新胜北路2459号</t>
+          <t>安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>连续在档 8 期；本期存在高相似店名「AITO授权用户中心•通化新胜北路」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 8 期</t>
         </is>
       </c>
     </row>
@@ -12009,27 +11849,27 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•通化新胜北路</t>
+          <t>鸿蒙智行尚界用户中心•淮北寇湾汽车城</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>通化市</t>
+          <t>淮北市</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>吉林省通化市新胜北路2459号</t>
+          <t>安徽省淮北市相山区任圩街道寇湾汽车城骏驰路3号201室</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>连续在档 8 期；本期存在高相似店名「AITO授权用户中心•通化新胜北路」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 8 期</t>
         </is>
       </c>
     </row>
@@ -12041,22 +11881,22 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•宿州经开区</t>
+          <t>AITO授权用户中心•兰州南滨河中路</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>宿州市</t>
+          <t>兰州市</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>安徽省宿州市埇桥区西昌南路与鞋城一路交汇处东南角</t>
+          <t>甘肃省兰州市七里河区南滨河中路上河苑409号</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -12073,89 +11913,25 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•淮北寇湾汽车城</t>
+          <t>华为授权体验店（未来方舟）</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>淮北市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>安徽省淮北市相山区任圩街道寇湾汽车城骏驰路3号201室</t>
+          <t>贵州省贵阳市云岩区未来方舟G6组团一号电梯旁华为授权体验店</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>连续在档 8 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•兰州南滨河中路</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>甘肃</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>兰州市</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>甘肃省兰州市七里河区南滨河中路上河苑409号</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>连续在档 8 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>华为授权体验店（未来方舟）</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>贵阳市</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>贵州省贵阳市云岩区未来方舟G6组团一号电梯旁华为授权体验店</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>连续在档 8 期</t>
         </is>
@@ -12172,7 +11948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12218,22 +11994,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•昆明南亚风情第壹城</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12243,7 +12019,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆 → 云南省昆明市西山区滇池路569号滇池南亚风情第壹城F1</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12031,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12275,29 +12051,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•衡水昌明街</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12307,14 +12083,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新技术开发区胜利西路2088号1幢103号 → 河北省衡水市昌明大街与胜利路交叉口转盘西南角西行100米</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -12324,12 +12100,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12339,14 +12115,14 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -12356,12 +12132,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12371,7 +12147,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米 → 广东省佛山市禅城区石湾镇街道佛山大道12号世纪德远车华里3座（临时营业）</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12388,12 +12164,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12403,29 +12179,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12435,29 +12211,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C院 → 江西省南昌市青山湖区高新大道708号C座</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12467,29 +12243,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12499,29 +12275,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区东长安街神州三路399号 → 陕西省西安市长安区航天基地东长安街399号</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•保定朝阳北大街</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12531,29 +12307,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市竞秀区朝阳北大街1218号 → 河北省保定市高开区朝阳北大街1218号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12563,29 +12339,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层 → 四川省眉山市东坡区眉州大道西五段99号1-1层</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12595,7 +12371,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代4S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代5S店院内）</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
@@ -12607,17 +12383,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•湘潭九华</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12627,29 +12403,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>湖南省湘潭市经开区湘望路2号 → 湖南省湘潭市雨湖区S41长潭西高速出口与S41长潭西高速交叉口西140米</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>成都仁和新城城市展厅109</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12659,551 +12435,71 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>南昌红谷滩万象天地新能源空间</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>南昌红谷滩印象城新能源空间</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号 → 河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车常德大道销售中心</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车常德大道销售中心</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-01 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行智界用户中心•福州青口汽车城</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>福建省福州市闽侯县尚干镇新榕路1号汽车超市二层C区C204-C223 → 福建省福州市闽侯县尚干镇新榕路1号汽车超市二层A区A201-A205</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>吉林</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4539号 → 吉林省延边朝鲜族自治州延吉市长白山东路4765号</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>黑龙江</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>黑龙省大庆市高新区产业一区(新兴西街4号) → 黑龙江省大庆市龙凤区开发区新兴西街2-1号</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>广州（汕头）交付中心</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>广州科学城交付中心</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车泉州南服务中心</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•南网电动</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•海南电动</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>成都仁和新城城市展厅109</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>地址相似度 67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
           <t>店名相似度 76%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>沃尔沃</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>南昌红谷滩万象天地新能源空间</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>南昌红谷滩印象城新能源空间</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C18" s="4" t="n">
         <v>1451</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>1452</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>1</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8452</v>
+        <v>8451</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8445</v>
+        <v>8444</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-7</v>
@@ -9871,10 +9871,10 @@
         </is>
       </c>
       <c r="C427" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D427" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E427" s="2" t="n">
         <v>0</v>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆二郎销售中心</t>
+          <t>小鹏汽车重庆两江新区交付中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区石新路172号附2号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆两江新区交付中心</t>
+          <t>小鹏汽车重庆二郎销售中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>重庆市九龙坡区石新路172号附2号</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,29 +12051,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12083,14 +12083,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
@@ -12164,12 +12164,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12223,17 +12223,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12314,22 +12314,22 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（24家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（31家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（16条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（24家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（31家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（16条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆两江新区交付中心</t>
+          <t>小鹏汽车重庆二郎销售中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>重庆市九龙坡区石新路172号附2号</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆二郎销售中心</t>
+          <t>小鹏汽车重庆两江新区交付中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区石新路172号附2号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>东莞世奥</t>
+          <t>东莞捷世丰</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市南城区莞太大道石鼓路段</t>
+          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>东莞捷世丰</t>
+          <t>东莞世奥</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
+          <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>广州南菱奥申</t>
+          <t>广东广物金盈汽车贸易有限公司</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广花一路136号</t>
+          <t>广东省广州市白云区机场路898号</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>广东广物金盈汽车贸易有限公司</t>
+          <t>广州南菱奥申</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区机场路898号</t>
+          <t>广东省广州市白云区广花一路136号</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,14 +12051,14 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12223,17 +12223,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12243,14 +12243,14 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -12314,22 +12314,22 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12442,22 +12442,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩万象天地新能源空间</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩印象城新能源空间</t>
+          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12467,29 +12467,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>南昌红谷滩万象天地新能源空间</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
+          <t>南昌红谷滩印象城新能源空间</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -10953,7 +10953,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>东莞捷世丰</t>
+          <t>东莞世奥</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
+          <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>东莞世奥</t>
+          <t>东莞捷世丰</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市南城区莞太大道石鼓路段</t>
+          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>广东广物金盈汽车贸易有限公司</t>
+          <t>广州南菱奥申</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区机场路898号</t>
+          <t>广东省广州市白云区广花一路136号</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>广州南菱奥申</t>
+          <t>广东广物金盈汽车贸易有限公司</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广花一路136号</t>
+          <t>广东省广州市白云区机场路898号</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
@@ -12164,12 +12164,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12223,17 +12223,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12243,14 +12243,14 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,29 +12275,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12307,29 +12307,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12442,22 +12442,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>南昌红谷滩万象天地新能源空间</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
+          <t>南昌红谷滩印象城新能源空间</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12467,29 +12467,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩万象天地新能源空间</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩印象城新能源空间</t>
+          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（24家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（31家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（16条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（24家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（31家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（16条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆二郎销售中心</t>
+          <t>小鹏汽车重庆两江新区交付中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区石新路172号附2号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆两江新区交付中心</t>
+          <t>小鹏汽车重庆二郎销售中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>重庆市九龙坡区石新路172号附2号</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>东莞世奥</t>
+          <t>东莞捷世丰</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市南城区莞太大道石鼓路段</t>
+          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>东莞捷世丰</t>
+          <t>东莞世奥</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
+          <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>福建润通</t>
+          <t>福建华奥</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区高仕路2号</t>
+          <t>福建省福州市闽侯县尚干镇良安路20号</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>福建华奥</t>
+          <t>福建润通</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇良安路20号</t>
+          <t>福建省福州市仓山区高仕路2号</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -11994,7 +11994,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -12223,17 +12223,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,29 +12275,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12442,22 +12442,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩万象天地新能源空间</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩印象城新能源空间</t>
+          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12467,29 +12467,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>南昌红谷滩万象天地新能源空间</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
+          <t>南昌红谷滩印象城新能源空间</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（24家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（31家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（16条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（24家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（31家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（16条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>东莞捷世丰</t>
+          <t>东莞世奥</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
+          <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>东莞世奥</t>
+          <t>东莞捷世丰</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市南城区莞太大道石鼓路段</t>
+          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>佛山世锦</t>
+          <t>佛山广物君奥</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
+          <t>广东省佛山市禅城区佛山大道中路83号</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>佛山广物君奥</t>
+          <t>佛山世锦</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区佛山大道中路83号</t>
+          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>广州南菱奥申</t>
+          <t>广东广物金盈汽车贸易有限公司</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广花一路136号</t>
+          <t>广东省广州市白云区机场路898号</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>广东广物金盈汽车贸易有限公司</t>
+          <t>广州南菱奥申</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区机场路898号</t>
+          <t>广东省广州市白云区广花一路136号</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -11994,22 +11994,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12100,12 +12100,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
@@ -12218,22 +12218,22 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12287,17 +12287,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
@@ -12346,22 +12346,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12083,29 +12083,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12211,14 +12211,14 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -12228,12 +12228,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12292,12 +12292,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12307,29 +12307,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12442,22 +12442,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>南昌红谷滩万象天地新能源空间</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
+          <t>南昌红谷滩印象城新能源空间</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12467,29 +12467,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩万象天地新能源空间</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩印象城新能源空间</t>
+          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -11081,7 +11081,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>广东广物金盈汽车贸易有限公司</t>
+          <t>广州南菱奥申</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区机场路898号</t>
+          <t>广东省广州市白云区广花一路136号</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>广州南菱奥申</t>
+          <t>广东广物金盈汽车贸易有限公司</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广花一路136号</t>
+          <t>广东省广州市白云区机场路898号</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>福建华奥</t>
+          <t>福建润通</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇良安路20号</t>
+          <t>福建省福州市仓山区高仕路2号</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>福建润通</t>
+          <t>福建华奥</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区高仕路2号</t>
+          <t>福建省福州市闽侯县尚干镇良安路20号</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12083,29 +12083,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12179,29 +12179,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -12228,12 +12228,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12287,17 +12287,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12307,29 +12307,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12442,22 +12442,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩万象天地新能源空间</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩印象城新能源空间</t>
+          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12467,29 +12467,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>南昌红谷滩万象天地新能源空间</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
+          <t>南昌红谷滩印象城新能源空间</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -10579,7 +10579,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆两江新区交付中心</t>
+          <t>小鹏汽车重庆二郎销售中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>重庆市九龙坡区石新路172号附2号</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆二郎销售中心</t>
+          <t>小鹏汽车重庆两江新区交付中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区石新路172号附2号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>佛山广物君奥</t>
+          <t>佛山世锦</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区佛山大道中路83号</t>
+          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>佛山世锦</t>
+          <t>佛山广物君奥</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
+          <t>广东省佛山市禅城区佛山大道中路83号</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12132,12 +12132,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12186,22 +12186,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -12223,17 +12223,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,14 +12275,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -12292,12 +12292,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12307,29 +12307,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -10579,7 +10579,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆二郎销售中心</t>
+          <t>小鹏汽车重庆两江新区交付中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区石新路172号附2号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆两江新区交付中心</t>
+          <t>小鹏汽车重庆二郎销售中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>重庆市九龙坡区石新路172号附2号</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>佛山世锦</t>
+          <t>佛山广物君奥</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
+          <t>广东省佛山市禅城区佛山大道中路83号</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>佛山广物君奥</t>
+          <t>佛山世锦</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区佛山大道中路83号</t>
+          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>广州南菱奥申</t>
+          <t>广东广物金盈汽车贸易有限公司</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广花一路136号</t>
+          <t>广东省广州市白云区机场路898号</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>广东广物金盈汽车贸易有限公司</t>
+          <t>广州南菱奥申</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区机场路898号</t>
+          <t>广东省广州市白云区广花一路136号</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>福建润通</t>
+          <t>福建华奥</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区高仕路2号</t>
+          <t>福建省福州市闽侯县尚干镇良安路20号</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>福建华奥</t>
+          <t>福建润通</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇良安路20号</t>
+          <t>福建省福州市仓山区高仕路2号</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12100,12 +12100,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12179,29 +12179,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -12223,17 +12223,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,29 +12275,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12307,29 +12307,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12442,22 +12442,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>南昌红谷滩万象天地新能源空间</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
+          <t>南昌红谷滩印象城新能源空间</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12467,29 +12467,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩万象天地新能源空间</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩印象城新能源空间</t>
+          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
